--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123160707</v>
+        <v>123161094</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -709,9 +709,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fösan, Dlr</t>
@@ -721,10 +718,10 @@
         <v>501791</v>
       </c>
       <c r="R2" t="n">
-        <v>6762802</v>
+        <v>6762807</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,14 +780,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123161094</v>
+        <v>123160707</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -825,6 +821,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fösan, Dlr</t>
@@ -834,10 +833,10 @@
         <v>501791</v>
       </c>
       <c r="R3" t="n">
-        <v>6762807</v>
+        <v>6762802</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123161094</v>
+        <v>123160681</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123160681</v>
+        <v>123161094</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>123160707</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123161094</v>
+        <v>123160681</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>123160707</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123160681</v>
+        <v>123161094</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>123160707</v>
       </c>
       <c r="B3" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123161094</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123160707</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123161094</v>
       </c>
       <c r="B2" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>123160707</v>
       </c>
       <c r="B3" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123161094</v>
+        <v>123160707</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,6 +709,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fösan, Dlr</t>
@@ -718,10 +721,10 @@
         <v>501791</v>
       </c>
       <c r="R2" t="n">
-        <v>6762807</v>
+        <v>6762802</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,17 +784,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123160707</v>
+        <v>123161094</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,9 +825,6 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fösan, Dlr</t>
@@ -833,10 +834,10 @@
         <v>501791</v>
       </c>
       <c r="R3" t="n">
-        <v>6762802</v>
+        <v>6762807</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123160707</v>
+        <v>123161094</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -709,9 +709,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fösan, Dlr</t>
@@ -721,10 +718,10 @@
         <v>501791</v>
       </c>
       <c r="R2" t="n">
-        <v>6762802</v>
+        <v>6762807</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,17 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123161094</v>
+        <v>123160707</v>
       </c>
       <c r="B3" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,6 +821,9 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fösan, Dlr</t>
@@ -834,10 +833,10 @@
         <v>501791</v>
       </c>
       <c r="R3" t="n">
-        <v>6762807</v>
+        <v>6762802</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Anna-Britt Olsson, Rolf Lundqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,6 +901,2964 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125702431</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>501838</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6762713</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125702422</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>501789</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6762716</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125702420</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501790</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6762741</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125703106</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>501819</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6762675</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125702416</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>501889</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6762681</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125702421</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>501789</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6762721</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125702428</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>501808</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6762693</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125702425</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>501795</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6762667</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125702424</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>501784</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6762682</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125702432</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>501831</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6762704</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125702418</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>501855</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6762699</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125703107</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>501822</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6762686</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125702406</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>501805</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6762735</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125702430</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>501814</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6762691</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125703105</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>501807</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6762671</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125702452</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>501629</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6763012</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125702429</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>501822</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6762701</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125702426</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>501808</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6762679</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125702433</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>501852</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6762730</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125702419</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>501856</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6762707</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125702417</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>501886</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6762679</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125704112</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>501889</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6762650</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125704107</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>501862</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6762637</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125704109</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>501895</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6762621</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125704110</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>501900</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6762637</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125704106</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>501847</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6762643</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125704113</v>
+      </c>
+      <c r="B30" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>501816</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6762645</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>125704111</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>501886</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6762641</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125704108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>501881</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6762636</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -2261,7 +2261,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702419</v>
+        <v>125702426</v>
       </c>
       <c r="B18" t="n">
         <v>78967</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501856</v>
+        <v>501808</v>
       </c>
       <c r="R18" t="n">
-        <v>6762707</v>
+        <v>6762679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702426</v>
+        <v>125702419</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501808</v>
+        <v>501856</v>
       </c>
       <c r="R19" t="n">
-        <v>6762679</v>
+        <v>6762707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125703101</v>
+        <v>125703096</v>
       </c>
       <c r="B31" t="n">
         <v>78967</v>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501816</v>
+        <v>501871</v>
       </c>
       <c r="R31" t="n">
-        <v>6762645</v>
+        <v>6762693</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125703096</v>
+        <v>125703102</v>
       </c>
       <c r="B32" t="n">
         <v>78967</v>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501871</v>
+        <v>501806</v>
       </c>
       <c r="R32" t="n">
-        <v>6762693</v>
+        <v>6762648</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125703102</v>
+        <v>125703080</v>
       </c>
       <c r="B33" t="n">
         <v>78967</v>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501806</v>
+        <v>501862</v>
       </c>
       <c r="R33" t="n">
-        <v>6762648</v>
+        <v>6762637</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125703080</v>
+        <v>125703101</v>
       </c>
       <c r="B34" t="n">
         <v>78967</v>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501862</v>
+        <v>501816</v>
       </c>
       <c r="R34" t="n">
-        <v>6762637</v>
+        <v>6762645</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703098</v>
+        <v>125703100</v>
       </c>
       <c r="B43" t="n">
         <v>78967</v>
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>501833</v>
+        <v>501827</v>
       </c>
       <c r="R43" t="n">
-        <v>6762643</v>
+        <v>6762616</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703094</v>
+        <v>125703098</v>
       </c>
       <c r="B44" t="n">
         <v>78967</v>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501903</v>
+        <v>501833</v>
       </c>
       <c r="R44" t="n">
-        <v>6762639</v>
+        <v>6762643</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703100</v>
+        <v>125703094</v>
       </c>
       <c r="B45" t="n">
         <v>78967</v>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>501827</v>
+        <v>501903</v>
       </c>
       <c r="R45" t="n">
-        <v>6762616</v>
+        <v>6762639</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702418</v>
+        <v>125702421</v>
       </c>
       <c r="B6" t="n">
         <v>78967</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501855</v>
+        <v>501789</v>
       </c>
       <c r="R6" t="n">
-        <v>6762699</v>
+        <v>6762721</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125702421</v>
+        <v>125702418</v>
       </c>
       <c r="B7" t="n">
         <v>78967</v>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501789</v>
+        <v>501855</v>
       </c>
       <c r="R7" t="n">
-        <v>6762721</v>
+        <v>6762699</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702416</v>
+        <v>125702424</v>
       </c>
       <c r="B11" t="n">
         <v>78967</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501889</v>
+        <v>501784</v>
       </c>
       <c r="R11" t="n">
-        <v>6762681</v>
+        <v>6762682</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703107</v>
+        <v>125702428</v>
       </c>
       <c r="B12" t="n">
         <v>78967</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501822</v>
+        <v>501808</v>
       </c>
       <c r="R12" t="n">
-        <v>6762686</v>
+        <v>6762693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1776,7 +1776,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702424</v>
+        <v>125702416</v>
       </c>
       <c r="B13" t="n">
         <v>78967</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501784</v>
+        <v>501889</v>
       </c>
       <c r="R13" t="n">
-        <v>6762682</v>
+        <v>6762681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702428</v>
+        <v>125703107</v>
       </c>
       <c r="B14" t="n">
         <v>78967</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501808</v>
+        <v>501822</v>
       </c>
       <c r="R14" t="n">
-        <v>6762693</v>
+        <v>6762686</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2261,7 +2261,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702426</v>
+        <v>125702419</v>
       </c>
       <c r="B18" t="n">
         <v>78967</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501808</v>
+        <v>501856</v>
       </c>
       <c r="R18" t="n">
-        <v>6762679</v>
+        <v>6762707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702419</v>
+        <v>125702426</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501856</v>
+        <v>501808</v>
       </c>
       <c r="R19" t="n">
-        <v>6762707</v>
+        <v>6762679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125702429</v>
+        <v>125702431</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501822</v>
+        <v>501838</v>
       </c>
       <c r="R22" t="n">
-        <v>6762701</v>
+        <v>6762713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125702431</v>
+        <v>125702432</v>
       </c>
       <c r="B23" t="n">
         <v>78967</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501838</v>
+        <v>501831</v>
       </c>
       <c r="R23" t="n">
-        <v>6762713</v>
+        <v>6762704</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125702432</v>
+        <v>125702429</v>
       </c>
       <c r="B24" t="n">
         <v>78967</v>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501831</v>
+        <v>501822</v>
       </c>
       <c r="R24" t="n">
-        <v>6762704</v>
+        <v>6762701</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703086</v>
+        <v>125703081</v>
       </c>
       <c r="B26" t="n">
         <v>78967</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501883</v>
+        <v>501881</v>
       </c>
       <c r="R26" t="n">
-        <v>6762666</v>
+        <v>6762636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703081</v>
+        <v>125704110</v>
       </c>
       <c r="B27" t="n">
         <v>78967</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501881</v>
+        <v>501900</v>
       </c>
       <c r="R27" t="n">
-        <v>6762636</v>
+        <v>6762637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125704110</v>
+        <v>125703086</v>
       </c>
       <c r="B28" t="n">
         <v>78967</v>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501900</v>
+        <v>501883</v>
       </c>
       <c r="R28" t="n">
-        <v>6762637</v>
+        <v>6762666</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125703080</v>
+        <v>125703101</v>
       </c>
       <c r="B33" t="n">
         <v>78967</v>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501862</v>
+        <v>501816</v>
       </c>
       <c r="R33" t="n">
-        <v>6762637</v>
+        <v>6762645</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125703101</v>
+        <v>125703080</v>
       </c>
       <c r="B34" t="n">
         <v>78967</v>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501816</v>
+        <v>501862</v>
       </c>
       <c r="R34" t="n">
-        <v>6762645</v>
+        <v>6762637</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703087</v>
+        <v>125703104</v>
       </c>
       <c r="B39" t="n">
         <v>78967</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501873</v>
+        <v>501800</v>
       </c>
       <c r="R39" t="n">
-        <v>6762669</v>
+        <v>6762674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703088</v>
+        <v>125703087</v>
       </c>
       <c r="B40" t="n">
         <v>78967</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501841</v>
+        <v>501873</v>
       </c>
       <c r="R40" t="n">
-        <v>6762704</v>
+        <v>6762669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703104</v>
+        <v>125703088</v>
       </c>
       <c r="B41" t="n">
         <v>78967</v>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>501800</v>
+        <v>501841</v>
       </c>
       <c r="R41" t="n">
-        <v>6762674</v>
+        <v>6762704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703100</v>
+        <v>125703098</v>
       </c>
       <c r="B43" t="n">
         <v>78967</v>
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>501827</v>
+        <v>501833</v>
       </c>
       <c r="R43" t="n">
-        <v>6762616</v>
+        <v>6762643</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703098</v>
+        <v>125703100</v>
       </c>
       <c r="B44" t="n">
         <v>78967</v>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501833</v>
+        <v>501827</v>
       </c>
       <c r="R44" t="n">
-        <v>6762643</v>
+        <v>6762616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125703092</v>
+        <v>125703103</v>
       </c>
       <c r="B47" t="n">
         <v>78967</v>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>501896</v>
+        <v>501797</v>
       </c>
       <c r="R47" t="n">
-        <v>6762661</v>
+        <v>6762655</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125703103</v>
+        <v>125703092</v>
       </c>
       <c r="B48" t="n">
         <v>78967</v>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>501797</v>
+        <v>501896</v>
       </c>
       <c r="R48" t="n">
-        <v>6762655</v>
+        <v>6762661</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -3134,7 +3134,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125704110</v>
+        <v>125703086</v>
       </c>
       <c r="B27" t="n">
         <v>78967</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501900</v>
+        <v>501883</v>
       </c>
       <c r="R27" t="n">
-        <v>6762637</v>
+        <v>6762666</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125703086</v>
+        <v>125704110</v>
       </c>
       <c r="B28" t="n">
         <v>78967</v>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501883</v>
+        <v>501900</v>
       </c>
       <c r="R28" t="n">
-        <v>6762666</v>
+        <v>6762637</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -3134,7 +3134,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703086</v>
+        <v>125704110</v>
       </c>
       <c r="B27" t="n">
         <v>78967</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501883</v>
+        <v>501900</v>
       </c>
       <c r="R27" t="n">
-        <v>6762666</v>
+        <v>6762637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125704110</v>
+        <v>125703086</v>
       </c>
       <c r="B28" t="n">
         <v>78967</v>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501900</v>
+        <v>501883</v>
       </c>
       <c r="R28" t="n">
-        <v>6762637</v>
+        <v>6762666</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703104</v>
+        <v>125703087</v>
       </c>
       <c r="B39" t="n">
         <v>78967</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501800</v>
+        <v>501873</v>
       </c>
       <c r="R39" t="n">
-        <v>6762674</v>
+        <v>6762669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703087</v>
+        <v>125703088</v>
       </c>
       <c r="B40" t="n">
         <v>78967</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501873</v>
+        <v>501841</v>
       </c>
       <c r="R40" t="n">
-        <v>6762669</v>
+        <v>6762704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703088</v>
+        <v>125703104</v>
       </c>
       <c r="B41" t="n">
         <v>78967</v>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>501841</v>
+        <v>501800</v>
       </c>
       <c r="R41" t="n">
-        <v>6762704</v>
+        <v>6762674</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125703103</v>
+        <v>125703092</v>
       </c>
       <c r="B47" t="n">
         <v>78967</v>
@@ -5109,10 +5109,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>501797</v>
+        <v>501896</v>
       </c>
       <c r="R47" t="n">
-        <v>6762655</v>
+        <v>6762661</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125703092</v>
+        <v>125703103</v>
       </c>
       <c r="B48" t="n">
         <v>78967</v>
@@ -5206,10 +5206,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>501896</v>
+        <v>501797</v>
       </c>
       <c r="R48" t="n">
-        <v>6762661</v>
+        <v>6762655</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>125702433</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>125702420</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702421</v>
+        <v>125702418</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501789</v>
+        <v>501855</v>
       </c>
       <c r="R6" t="n">
-        <v>6762721</v>
+        <v>6762699</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125702418</v>
+        <v>125702421</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501855</v>
+        <v>501789</v>
       </c>
       <c r="R7" t="n">
-        <v>6762699</v>
+        <v>6762721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
         <v>125702406</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125702417</v>
+        <v>125702430</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501886</v>
+        <v>501814</v>
       </c>
       <c r="R9" t="n">
-        <v>6762679</v>
+        <v>6762691</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125702430</v>
+        <v>125702417</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501814</v>
+        <v>501886</v>
       </c>
       <c r="R10" t="n">
-        <v>6762691</v>
+        <v>6762679</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702424</v>
+        <v>125702428</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501784</v>
+        <v>501808</v>
       </c>
       <c r="R11" t="n">
-        <v>6762682</v>
+        <v>6762693</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702428</v>
+        <v>125703107</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501808</v>
+        <v>501822</v>
       </c>
       <c r="R12" t="n">
-        <v>6762693</v>
+        <v>6762686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1776,10 +1776,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702416</v>
+        <v>125702424</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501889</v>
+        <v>501784</v>
       </c>
       <c r="R13" t="n">
-        <v>6762681</v>
+        <v>6762682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703107</v>
+        <v>125702416</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501822</v>
+        <v>501889</v>
       </c>
       <c r="R14" t="n">
-        <v>6762686</v>
+        <v>6762681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1973,7 +1973,7 @@
         <v>125702452</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>125703106</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>125703105</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702419</v>
+        <v>125702426</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501856</v>
+        <v>501808</v>
       </c>
       <c r="R18" t="n">
-        <v>6762707</v>
+        <v>6762679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702426</v>
+        <v>125702419</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501808</v>
+        <v>501856</v>
       </c>
       <c r="R19" t="n">
-        <v>6762679</v>
+        <v>6762707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
         <v>125702422</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>125702425</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125702431</v>
+        <v>125702429</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501838</v>
+        <v>501822</v>
       </c>
       <c r="R22" t="n">
-        <v>6762713</v>
+        <v>6762701</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125702432</v>
+        <v>125702431</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501831</v>
+        <v>501838</v>
       </c>
       <c r="R23" t="n">
-        <v>6762704</v>
+        <v>6762713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,10 +2843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125702429</v>
+        <v>125702432</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501822</v>
+        <v>501831</v>
       </c>
       <c r="R24" t="n">
-        <v>6762701</v>
+        <v>6762704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2943,7 +2943,7 @@
         <v>125704109</v>
       </c>
       <c r="B25" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703081</v>
+        <v>125704110</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501881</v>
+        <v>501900</v>
       </c>
       <c r="R26" t="n">
-        <v>6762636</v>
+        <v>6762637</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125704110</v>
+        <v>125703081</v>
       </c>
       <c r="B27" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501900</v>
+        <v>501881</v>
       </c>
       <c r="R27" t="n">
-        <v>6762637</v>
+        <v>6762636</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3234,7 +3234,7 @@
         <v>125703086</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>125704424</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>125703097</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125703096</v>
+        <v>125703102</v>
       </c>
       <c r="B31" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501871</v>
+        <v>501806</v>
       </c>
       <c r="R31" t="n">
-        <v>6762693</v>
+        <v>6762648</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125703102</v>
+        <v>125703096</v>
       </c>
       <c r="B32" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501806</v>
+        <v>501871</v>
       </c>
       <c r="R32" t="n">
-        <v>6762648</v>
+        <v>6762693</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3719,7 +3719,7 @@
         <v>125703101</v>
       </c>
       <c r="B33" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>125703080</v>
       </c>
       <c r="B34" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>125703095</v>
       </c>
       <c r="B35" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>125704111</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>125703079</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>125703091</v>
       </c>
       <c r="B38" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125703087</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703088</v>
+        <v>125703104</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501841</v>
+        <v>501800</v>
       </c>
       <c r="R40" t="n">
-        <v>6762704</v>
+        <v>6762674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703104</v>
+        <v>125703088</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>501800</v>
+        <v>501841</v>
       </c>
       <c r="R41" t="n">
-        <v>6762674</v>
+        <v>6762704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4592,7 +4592,7 @@
         <v>125703093</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703098</v>
+        <v>125703094</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>501833</v>
+        <v>501903</v>
       </c>
       <c r="R43" t="n">
-        <v>6762643</v>
+        <v>6762639</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4783,10 +4783,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703100</v>
+        <v>125703098</v>
       </c>
       <c r="B44" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501827</v>
+        <v>501833</v>
       </c>
       <c r="R44" t="n">
-        <v>6762616</v>
+        <v>6762643</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703094</v>
+        <v>125703100</v>
       </c>
       <c r="B45" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>501903</v>
+        <v>501827</v>
       </c>
       <c r="R45" t="n">
-        <v>6762639</v>
+        <v>6762616</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
         <v>125703099</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>125703092</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>125703103</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>125703090</v>
       </c>
       <c r="B49" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>125702433</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>125702420</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>125702418</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>125702421</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>125702406</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125702430</v>
+        <v>125702417</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501814</v>
+        <v>501886</v>
       </c>
       <c r="R9" t="n">
-        <v>6762691</v>
+        <v>6762679</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125702417</v>
+        <v>125702430</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501886</v>
+        <v>501814</v>
       </c>
       <c r="R10" t="n">
-        <v>6762679</v>
+        <v>6762691</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702428</v>
+        <v>125702424</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501808</v>
+        <v>501784</v>
       </c>
       <c r="R11" t="n">
-        <v>6762693</v>
+        <v>6762682</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703107</v>
+        <v>125702428</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501822</v>
+        <v>501808</v>
       </c>
       <c r="R12" t="n">
-        <v>6762686</v>
+        <v>6762693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1776,10 +1776,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702424</v>
+        <v>125702416</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501784</v>
+        <v>501889</v>
       </c>
       <c r="R13" t="n">
-        <v>6762682</v>
+        <v>6762681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702416</v>
+        <v>125703107</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501889</v>
+        <v>501822</v>
       </c>
       <c r="R14" t="n">
-        <v>6762681</v>
+        <v>6762686</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1973,7 +1973,7 @@
         <v>125702452</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>125703106</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>125703105</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702426</v>
+        <v>125702419</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501808</v>
+        <v>501856</v>
       </c>
       <c r="R18" t="n">
-        <v>6762679</v>
+        <v>6762707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702419</v>
+        <v>125702426</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501856</v>
+        <v>501808</v>
       </c>
       <c r="R19" t="n">
-        <v>6762707</v>
+        <v>6762679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
         <v>125702422</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>125702425</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>125702429</v>
       </c>
       <c r="B22" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>125702431</v>
       </c>
       <c r="B23" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>125702432</v>
       </c>
       <c r="B24" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>125704109</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>125704110</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>125703081</v>
       </c>
       <c r="B27" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>125703086</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>125704424</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>125703097</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125703102</v>
+        <v>125703101</v>
       </c>
       <c r="B31" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501806</v>
+        <v>501816</v>
       </c>
       <c r="R31" t="n">
-        <v>6762648</v>
+        <v>6762645</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125703096</v>
+        <v>125703080</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501871</v>
+        <v>501862</v>
       </c>
       <c r="R32" t="n">
-        <v>6762693</v>
+        <v>6762637</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,10 +3716,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125703101</v>
+        <v>125703096</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501816</v>
+        <v>501871</v>
       </c>
       <c r="R33" t="n">
-        <v>6762645</v>
+        <v>6762693</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125703080</v>
+        <v>125703102</v>
       </c>
       <c r="B34" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501862</v>
+        <v>501806</v>
       </c>
       <c r="R34" t="n">
-        <v>6762637</v>
+        <v>6762648</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
         <v>125703095</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>125704111</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>125703079</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>125703091</v>
       </c>
       <c r="B38" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703087</v>
+        <v>125703104</v>
       </c>
       <c r="B39" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501873</v>
+        <v>501800</v>
       </c>
       <c r="R39" t="n">
-        <v>6762669</v>
+        <v>6762674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703104</v>
+        <v>125703087</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501800</v>
+        <v>501873</v>
       </c>
       <c r="R40" t="n">
-        <v>6762674</v>
+        <v>6762669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4495,7 +4495,7 @@
         <v>125703088</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>125703093</v>
       </c>
       <c r="B42" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>125703094</v>
       </c>
       <c r="B43" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703098</v>
+        <v>125703100</v>
       </c>
       <c r="B44" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501833</v>
+        <v>501827</v>
       </c>
       <c r="R44" t="n">
-        <v>6762643</v>
+        <v>6762616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703100</v>
+        <v>125703098</v>
       </c>
       <c r="B45" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>501827</v>
+        <v>501833</v>
       </c>
       <c r="R45" t="n">
-        <v>6762616</v>
+        <v>6762643</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
         <v>125703099</v>
       </c>
       <c r="B46" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>125703092</v>
       </c>
       <c r="B47" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>125703103</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>125703090</v>
       </c>
       <c r="B49" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125702433</v>
+        <v>125702420</v>
       </c>
       <c r="B4" t="n">
         <v>78972</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501852</v>
+        <v>501790</v>
       </c>
       <c r="R4" t="n">
-        <v>6762730</v>
+        <v>6762741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702420</v>
+        <v>125702433</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501790</v>
+        <v>501852</v>
       </c>
       <c r="R5" t="n">
-        <v>6762741</v>
+        <v>6762730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1582,7 +1582,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702424</v>
+        <v>125703107</v>
       </c>
       <c r="B11" t="n">
         <v>78972</v>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501784</v>
+        <v>501822</v>
       </c>
       <c r="R11" t="n">
-        <v>6762682</v>
+        <v>6762686</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1679,7 +1679,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702428</v>
+        <v>125702416</v>
       </c>
       <c r="B12" t="n">
         <v>78972</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501808</v>
+        <v>501889</v>
       </c>
       <c r="R12" t="n">
-        <v>6762693</v>
+        <v>6762681</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702416</v>
+        <v>125702424</v>
       </c>
       <c r="B13" t="n">
         <v>78972</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501889</v>
+        <v>501784</v>
       </c>
       <c r="R13" t="n">
-        <v>6762681</v>
+        <v>6762682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703107</v>
+        <v>125702428</v>
       </c>
       <c r="B14" t="n">
         <v>78972</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501822</v>
+        <v>501808</v>
       </c>
       <c r="R14" t="n">
-        <v>6762686</v>
+        <v>6762693</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,7 +2067,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703106</v>
+        <v>125703105</v>
       </c>
       <c r="B16" t="n">
         <v>78972</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501819</v>
+        <v>501807</v>
       </c>
       <c r="R16" t="n">
-        <v>6762675</v>
+        <v>6762671</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703105</v>
+        <v>125703106</v>
       </c>
       <c r="B17" t="n">
         <v>78972</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501807</v>
+        <v>501819</v>
       </c>
       <c r="R17" t="n">
-        <v>6762671</v>
+        <v>6762675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702419</v>
+        <v>125702426</v>
       </c>
       <c r="B18" t="n">
         <v>78972</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501856</v>
+        <v>501808</v>
       </c>
       <c r="R18" t="n">
-        <v>6762707</v>
+        <v>6762679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702426</v>
+        <v>125702419</v>
       </c>
       <c r="B19" t="n">
         <v>78972</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501808</v>
+        <v>501856</v>
       </c>
       <c r="R19" t="n">
-        <v>6762679</v>
+        <v>6762707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125702431</v>
+        <v>125702432</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501838</v>
+        <v>501831</v>
       </c>
       <c r="R23" t="n">
-        <v>6762713</v>
+        <v>6762704</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125702432</v>
+        <v>125702431</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501831</v>
+        <v>501838</v>
       </c>
       <c r="R24" t="n">
-        <v>6762704</v>
+        <v>6762713</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125704110</v>
+        <v>125703081</v>
       </c>
       <c r="B26" t="n">
         <v>78972</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501900</v>
+        <v>501881</v>
       </c>
       <c r="R26" t="n">
-        <v>6762637</v>
+        <v>6762636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703081</v>
+        <v>125704110</v>
       </c>
       <c r="B27" t="n">
         <v>78972</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501881</v>
+        <v>501900</v>
       </c>
       <c r="R27" t="n">
-        <v>6762636</v>
+        <v>6762637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125703101</v>
+        <v>125703102</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501816</v>
+        <v>501806</v>
       </c>
       <c r="R31" t="n">
-        <v>6762645</v>
+        <v>6762648</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125703080</v>
+        <v>125703101</v>
       </c>
       <c r="B32" t="n">
         <v>78972</v>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501862</v>
+        <v>501816</v>
       </c>
       <c r="R32" t="n">
-        <v>6762637</v>
+        <v>6762645</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125703096</v>
+        <v>125703080</v>
       </c>
       <c r="B33" t="n">
         <v>78972</v>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501871</v>
+        <v>501862</v>
       </c>
       <c r="R33" t="n">
-        <v>6762693</v>
+        <v>6762637</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125703102</v>
+        <v>125703096</v>
       </c>
       <c r="B34" t="n">
         <v>78972</v>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501806</v>
+        <v>501871</v>
       </c>
       <c r="R34" t="n">
-        <v>6762648</v>
+        <v>6762693</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703104</v>
+        <v>125703087</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501800</v>
+        <v>501873</v>
       </c>
       <c r="R39" t="n">
-        <v>6762674</v>
+        <v>6762669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703087</v>
+        <v>125703104</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501873</v>
+        <v>501800</v>
       </c>
       <c r="R40" t="n">
-        <v>6762669</v>
+        <v>6762674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703100</v>
+        <v>125703098</v>
       </c>
       <c r="B44" t="n">
         <v>78972</v>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501827</v>
+        <v>501833</v>
       </c>
       <c r="R44" t="n">
-        <v>6762616</v>
+        <v>6762643</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703098</v>
+        <v>125703100</v>
       </c>
       <c r="B45" t="n">
         <v>78972</v>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>501833</v>
+        <v>501827</v>
       </c>
       <c r="R45" t="n">
-        <v>6762643</v>
+        <v>6762616</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125702420</v>
+        <v>125702433</v>
       </c>
       <c r="B4" t="n">
         <v>78972</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501790</v>
+        <v>501852</v>
       </c>
       <c r="R4" t="n">
-        <v>6762741</v>
+        <v>6762730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702433</v>
+        <v>125702420</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501852</v>
+        <v>501790</v>
       </c>
       <c r="R5" t="n">
-        <v>6762730</v>
+        <v>6762741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703087</v>
+        <v>125703104</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501873</v>
+        <v>501800</v>
       </c>
       <c r="R39" t="n">
-        <v>6762669</v>
+        <v>6762674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703104</v>
+        <v>125703088</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501800</v>
+        <v>501841</v>
       </c>
       <c r="R40" t="n">
-        <v>6762674</v>
+        <v>6762704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703088</v>
+        <v>125703087</v>
       </c>
       <c r="B41" t="n">
         <v>78972</v>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>501841</v>
+        <v>501873</v>
       </c>
       <c r="R41" t="n">
-        <v>6762704</v>
+        <v>6762669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125702433</v>
+        <v>125702420</v>
       </c>
       <c r="B4" t="n">
         <v>78972</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501852</v>
+        <v>501790</v>
       </c>
       <c r="R4" t="n">
-        <v>6762730</v>
+        <v>6762741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702420</v>
+        <v>125702433</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501790</v>
+        <v>501852</v>
       </c>
       <c r="R5" t="n">
-        <v>6762741</v>
+        <v>6762730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703105</v>
+        <v>125703106</v>
       </c>
       <c r="B16" t="n">
         <v>78972</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501807</v>
+        <v>501819</v>
       </c>
       <c r="R16" t="n">
-        <v>6762671</v>
+        <v>6762675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703106</v>
+        <v>125703105</v>
       </c>
       <c r="B17" t="n">
         <v>78972</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501819</v>
+        <v>501807</v>
       </c>
       <c r="R17" t="n">
-        <v>6762675</v>
+        <v>6762671</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125702429</v>
+        <v>125702431</v>
       </c>
       <c r="B22" t="n">
         <v>78972</v>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501822</v>
+        <v>501838</v>
       </c>
       <c r="R22" t="n">
-        <v>6762701</v>
+        <v>6762713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125702432</v>
+        <v>125702429</v>
       </c>
       <c r="B23" t="n">
         <v>78972</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501831</v>
+        <v>501822</v>
       </c>
       <c r="R23" t="n">
-        <v>6762704</v>
+        <v>6762701</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125702431</v>
+        <v>125702432</v>
       </c>
       <c r="B24" t="n">
         <v>78972</v>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501838</v>
+        <v>501831</v>
       </c>
       <c r="R24" t="n">
-        <v>6762713</v>
+        <v>6762704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125703102</v>
+        <v>125703096</v>
       </c>
       <c r="B31" t="n">
         <v>78972</v>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501806</v>
+        <v>501871</v>
       </c>
       <c r="R31" t="n">
-        <v>6762648</v>
+        <v>6762693</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125703101</v>
+        <v>125703102</v>
       </c>
       <c r="B32" t="n">
         <v>78972</v>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501816</v>
+        <v>501806</v>
       </c>
       <c r="R32" t="n">
-        <v>6762645</v>
+        <v>6762648</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125703080</v>
+        <v>125703101</v>
       </c>
       <c r="B33" t="n">
         <v>78972</v>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501862</v>
+        <v>501816</v>
       </c>
       <c r="R33" t="n">
-        <v>6762637</v>
+        <v>6762645</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125703096</v>
+        <v>125703080</v>
       </c>
       <c r="B34" t="n">
         <v>78972</v>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501871</v>
+        <v>501862</v>
       </c>
       <c r="R34" t="n">
-        <v>6762693</v>
+        <v>6762637</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703104</v>
+        <v>125703087</v>
       </c>
       <c r="B39" t="n">
         <v>78972</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501800</v>
+        <v>501873</v>
       </c>
       <c r="R39" t="n">
-        <v>6762674</v>
+        <v>6762669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703088</v>
+        <v>125703104</v>
       </c>
       <c r="B40" t="n">
         <v>78972</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501841</v>
+        <v>501800</v>
       </c>
       <c r="R40" t="n">
-        <v>6762704</v>
+        <v>6762674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703087</v>
+        <v>125703088</v>
       </c>
       <c r="B41" t="n">
         <v>78972</v>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>501873</v>
+        <v>501841</v>
       </c>
       <c r="R41" t="n">
-        <v>6762669</v>
+        <v>6762704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125702420</v>
+        <v>125702433</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501790</v>
+        <v>501852</v>
       </c>
       <c r="R4" t="n">
-        <v>6762741</v>
+        <v>6762730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702433</v>
+        <v>125702420</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501852</v>
+        <v>501790</v>
       </c>
       <c r="R5" t="n">
-        <v>6762730</v>
+        <v>6762741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
         <v>125702418</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>125702421</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>125702406</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125702417</v>
+        <v>125702430</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501886</v>
+        <v>501814</v>
       </c>
       <c r="R9" t="n">
-        <v>6762679</v>
+        <v>6762691</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125702430</v>
+        <v>125702417</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501814</v>
+        <v>501886</v>
       </c>
       <c r="R10" t="n">
-        <v>6762691</v>
+        <v>6762679</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125703107</v>
+        <v>125702424</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1617,10 +1617,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501822</v>
+        <v>501784</v>
       </c>
       <c r="R11" t="n">
-        <v>6762686</v>
+        <v>6762682</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1679,10 +1679,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702416</v>
+        <v>125702428</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501889</v>
+        <v>501808</v>
       </c>
       <c r="R12" t="n">
-        <v>6762681</v>
+        <v>6762693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,10 +1776,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702424</v>
+        <v>125702416</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501784</v>
+        <v>501889</v>
       </c>
       <c r="R13" t="n">
-        <v>6762682</v>
+        <v>6762681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702428</v>
+        <v>125703107</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501808</v>
+        <v>501822</v>
       </c>
       <c r="R14" t="n">
-        <v>6762693</v>
+        <v>6762686</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1973,7 +1973,7 @@
         <v>125702452</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>125703106</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>125703105</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702426</v>
+        <v>125702419</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501808</v>
+        <v>501856</v>
       </c>
       <c r="R18" t="n">
-        <v>6762679</v>
+        <v>6762707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,10 +2358,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702419</v>
+        <v>125702426</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501856</v>
+        <v>501808</v>
       </c>
       <c r="R19" t="n">
-        <v>6762707</v>
+        <v>6762679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2458,7 +2458,7 @@
         <v>125702422</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>125702425</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125702431</v>
+        <v>125702429</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501838</v>
+        <v>501822</v>
       </c>
       <c r="R22" t="n">
-        <v>6762713</v>
+        <v>6762701</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125702429</v>
+        <v>125702431</v>
       </c>
       <c r="B23" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501822</v>
+        <v>501838</v>
       </c>
       <c r="R23" t="n">
-        <v>6762701</v>
+        <v>6762713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
         <v>125702432</v>
       </c>
       <c r="B24" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>125704109</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>125703081</v>
       </c>
       <c r="B26" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>125704110</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>125703086</v>
       </c>
       <c r="B28" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>125704424</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>125703097</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>125703096</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>125703102</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>125703101</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>125703080</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>125703095</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>125704111</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>125703079</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>125703091</v>
       </c>
       <c r="B38" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4298,10 +4298,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703087</v>
+        <v>125703104</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501873</v>
+        <v>501800</v>
       </c>
       <c r="R39" t="n">
-        <v>6762669</v>
+        <v>6762674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703104</v>
+        <v>125703087</v>
       </c>
       <c r="B40" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501800</v>
+        <v>501873</v>
       </c>
       <c r="R40" t="n">
-        <v>6762674</v>
+        <v>6762669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4495,7 +4495,7 @@
         <v>125703088</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>125703093</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125703094</v>
+        <v>125703098</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4721,10 +4721,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>501903</v>
+        <v>501833</v>
       </c>
       <c r="R43" t="n">
-        <v>6762639</v>
+        <v>6762643</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4783,10 +4783,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703098</v>
+        <v>125703094</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501833</v>
+        <v>501903</v>
       </c>
       <c r="R44" t="n">
-        <v>6762643</v>
+        <v>6762639</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4883,7 +4883,7 @@
         <v>125703100</v>
       </c>
       <c r="B45" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>125703099</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>125703092</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>125703103</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>125703090</v>
       </c>
       <c r="B49" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125702433</v>
+        <v>125702420</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501852</v>
+        <v>501790</v>
       </c>
       <c r="R4" t="n">
-        <v>6762730</v>
+        <v>6762741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702420</v>
+        <v>125702433</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501790</v>
+        <v>501852</v>
       </c>
       <c r="R5" t="n">
-        <v>6762741</v>
+        <v>6762730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703106</v>
+        <v>125703105</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501819</v>
+        <v>501807</v>
       </c>
       <c r="R16" t="n">
-        <v>6762675</v>
+        <v>6762671</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703105</v>
+        <v>125703106</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501807</v>
+        <v>501819</v>
       </c>
       <c r="R17" t="n">
-        <v>6762671</v>
+        <v>6762675</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2261,7 +2261,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702419</v>
+        <v>125702426</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501856</v>
+        <v>501808</v>
       </c>
       <c r="R18" t="n">
-        <v>6762707</v>
+        <v>6762679</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702426</v>
+        <v>125702419</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501808</v>
+        <v>501856</v>
       </c>
       <c r="R19" t="n">
-        <v>6762679</v>
+        <v>6762707</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703081</v>
+        <v>125704110</v>
       </c>
       <c r="B26" t="n">
         <v>78973</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501881</v>
+        <v>501900</v>
       </c>
       <c r="R26" t="n">
-        <v>6762636</v>
+        <v>6762637</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125704110</v>
+        <v>125703081</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501900</v>
+        <v>501881</v>
       </c>
       <c r="R27" t="n">
-        <v>6762637</v>
+        <v>6762636</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703104</v>
+        <v>125703087</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501800</v>
+        <v>501873</v>
       </c>
       <c r="R39" t="n">
-        <v>6762674</v>
+        <v>6762669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703087</v>
+        <v>125703104</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501873</v>
+        <v>501800</v>
       </c>
       <c r="R40" t="n">
-        <v>6762669</v>
+        <v>6762674</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -2261,7 +2261,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702426</v>
+        <v>125702419</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501808</v>
+        <v>501856</v>
       </c>
       <c r="R18" t="n">
-        <v>6762679</v>
+        <v>6762707</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702419</v>
+        <v>125702426</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501856</v>
+        <v>501808</v>
       </c>
       <c r="R19" t="n">
-        <v>6762707</v>
+        <v>6762679</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702418</v>
+        <v>125702421</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501855</v>
+        <v>501789</v>
       </c>
       <c r="R6" t="n">
-        <v>6762699</v>
+        <v>6762721</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125702421</v>
+        <v>125702418</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501789</v>
+        <v>501855</v>
       </c>
       <c r="R7" t="n">
-        <v>6762721</v>
+        <v>6762699</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702428</v>
+        <v>125703107</v>
       </c>
       <c r="B12" t="n">
         <v>78973</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501808</v>
+        <v>501822</v>
       </c>
       <c r="R12" t="n">
-        <v>6762693</v>
+        <v>6762686</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1776,7 +1776,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702416</v>
+        <v>125702428</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501889</v>
+        <v>501808</v>
       </c>
       <c r="R13" t="n">
-        <v>6762681</v>
+        <v>6762693</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125703107</v>
+        <v>125702416</v>
       </c>
       <c r="B14" t="n">
         <v>78973</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501822</v>
+        <v>501889</v>
       </c>
       <c r="R14" t="n">
-        <v>6762686</v>
+        <v>6762681</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2067,7 +2067,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125703105</v>
+        <v>125703106</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501807</v>
+        <v>501819</v>
       </c>
       <c r="R16" t="n">
-        <v>6762671</v>
+        <v>6762675</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125703106</v>
+        <v>125703105</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501819</v>
+        <v>501807</v>
       </c>
       <c r="R17" t="n">
-        <v>6762675</v>
+        <v>6762671</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125702429</v>
+        <v>125702432</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501822</v>
+        <v>501831</v>
       </c>
       <c r="R22" t="n">
-        <v>6762701</v>
+        <v>6762704</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125702431</v>
+        <v>125702429</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501838</v>
+        <v>501822</v>
       </c>
       <c r="R23" t="n">
-        <v>6762713</v>
+        <v>6762701</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125702432</v>
+        <v>125702431</v>
       </c>
       <c r="B24" t="n">
         <v>78973</v>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501831</v>
+        <v>501838</v>
       </c>
       <c r="R24" t="n">
-        <v>6762704</v>
+        <v>6762713</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3037,7 +3037,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125704110</v>
+        <v>125703086</v>
       </c>
       <c r="B26" t="n">
         <v>78973</v>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501900</v>
+        <v>501883</v>
       </c>
       <c r="R26" t="n">
-        <v>6762637</v>
+        <v>6762666</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125703086</v>
+        <v>125704110</v>
       </c>
       <c r="B28" t="n">
         <v>78973</v>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501883</v>
+        <v>501900</v>
       </c>
       <c r="R28" t="n">
-        <v>6762666</v>
+        <v>6762637</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125703096</v>
+        <v>125703101</v>
       </c>
       <c r="B31" t="n">
         <v>78973</v>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501871</v>
+        <v>501816</v>
       </c>
       <c r="R31" t="n">
-        <v>6762693</v>
+        <v>6762645</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125703102</v>
+        <v>125703080</v>
       </c>
       <c r="B32" t="n">
         <v>78973</v>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501806</v>
+        <v>501862</v>
       </c>
       <c r="R32" t="n">
-        <v>6762648</v>
+        <v>6762637</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125703101</v>
+        <v>125703096</v>
       </c>
       <c r="B33" t="n">
         <v>78973</v>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501816</v>
+        <v>501871</v>
       </c>
       <c r="R33" t="n">
-        <v>6762645</v>
+        <v>6762693</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125703080</v>
+        <v>125703102</v>
       </c>
       <c r="B34" t="n">
         <v>78973</v>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501862</v>
+        <v>501806</v>
       </c>
       <c r="R34" t="n">
-        <v>6762637</v>
+        <v>6762648</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4298,7 +4298,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125703087</v>
+        <v>125703104</v>
       </c>
       <c r="B39" t="n">
         <v>78973</v>
@@ -4333,10 +4333,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>501873</v>
+        <v>501800</v>
       </c>
       <c r="R39" t="n">
-        <v>6762669</v>
+        <v>6762674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4395,7 +4395,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703104</v>
+        <v>125703088</v>
       </c>
       <c r="B40" t="n">
         <v>78973</v>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501800</v>
+        <v>501841</v>
       </c>
       <c r="R40" t="n">
-        <v>6762674</v>
+        <v>6762704</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,7 +4492,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703088</v>
+        <v>125703087</v>
       </c>
       <c r="B41" t="n">
         <v>78973</v>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>501841</v>
+        <v>501873</v>
       </c>
       <c r="R41" t="n">
-        <v>6762704</v>
+        <v>6762669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703094</v>
+        <v>125703100</v>
       </c>
       <c r="B44" t="n">
         <v>78973</v>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501903</v>
+        <v>501827</v>
       </c>
       <c r="R44" t="n">
-        <v>6762639</v>
+        <v>6762616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703100</v>
+        <v>125703094</v>
       </c>
       <c r="B45" t="n">
         <v>78973</v>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>501827</v>
+        <v>501903</v>
       </c>
       <c r="R45" t="n">
-        <v>6762616</v>
+        <v>6762639</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125702420</v>
+        <v>125702433</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501790</v>
+        <v>501852</v>
       </c>
       <c r="R4" t="n">
-        <v>6762741</v>
+        <v>6762730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702433</v>
+        <v>125702420</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501852</v>
+        <v>501790</v>
       </c>
       <c r="R5" t="n">
-        <v>6762730</v>
+        <v>6762741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 11320-2025 artfynd.xlsx
+++ b/artfynd/A 11320-2025 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>125702433</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>125702420</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702421</v>
+        <v>125702418</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501789</v>
+        <v>501855</v>
       </c>
       <c r="R6" t="n">
-        <v>6762721</v>
+        <v>6762699</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125702418</v>
+        <v>125702421</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501855</v>
+        <v>501789</v>
       </c>
       <c r="R7" t="n">
-        <v>6762699</v>
+        <v>6762721</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,7 +1294,7 @@
         <v>125702406</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>125702430</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>125702417</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>125702424</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125703107</v>
+        <v>125702428</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501822</v>
+        <v>501808</v>
       </c>
       <c r="R12" t="n">
-        <v>6762686</v>
+        <v>6762693</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1776,10 +1776,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702428</v>
+        <v>125702416</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1811,10 +1811,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501808</v>
+        <v>501889</v>
       </c>
       <c r="R13" t="n">
-        <v>6762693</v>
+        <v>6762681</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1873,10 +1873,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702416</v>
+        <v>125703107</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501889</v>
+        <v>501822</v>
       </c>
       <c r="R14" t="n">
-        <v>6762681</v>
+        <v>6762686</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1973,7 +1973,7 @@
         <v>125702452</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>125703106</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>125703105</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>125702419</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>125702426</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>125702422</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         <v>125702425</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125702432</v>
+        <v>125702429</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>501831</v>
+        <v>501822</v>
       </c>
       <c r="R22" t="n">
-        <v>6762704</v>
+        <v>6762701</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,10 +2746,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125702429</v>
+        <v>125702431</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>501822</v>
+        <v>501838</v>
       </c>
       <c r="R23" t="n">
-        <v>6762701</v>
+        <v>6762713</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2843,10 +2843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125702431</v>
+        <v>125702432</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>501838</v>
+        <v>501831</v>
       </c>
       <c r="R24" t="n">
-        <v>6762713</v>
+        <v>6762704</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2943,7 +2943,7 @@
         <v>125704109</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3037,10 +3037,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125703086</v>
+        <v>125703081</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>501883</v>
+        <v>501881</v>
       </c>
       <c r="R26" t="n">
-        <v>6762666</v>
+        <v>6762636</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3134,10 +3134,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125703081</v>
+        <v>125704110</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3169,10 +3169,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>501881</v>
+        <v>501900</v>
       </c>
       <c r="R27" t="n">
-        <v>6762636</v>
+        <v>6762637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3231,10 +3231,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125704110</v>
+        <v>125703086</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>501900</v>
+        <v>501883</v>
       </c>
       <c r="R28" t="n">
-        <v>6762637</v>
+        <v>6762666</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
         <v>125704424</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>125703097</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125703101</v>
+        <v>125703096</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>501816</v>
+        <v>501871</v>
       </c>
       <c r="R31" t="n">
-        <v>6762645</v>
+        <v>6762693</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3619,10 +3619,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125703080</v>
+        <v>125703102</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>501862</v>
+        <v>501806</v>
       </c>
       <c r="R32" t="n">
-        <v>6762637</v>
+        <v>6762648</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3716,10 +3716,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125703096</v>
+        <v>125703101</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>501871</v>
+        <v>501816</v>
       </c>
       <c r="R33" t="n">
-        <v>6762693</v>
+        <v>6762645</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3813,10 +3813,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125703102</v>
+        <v>125703080</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>501806</v>
+        <v>501862</v>
       </c>
       <c r="R34" t="n">
-        <v>6762648</v>
+        <v>6762637</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3913,7 +3913,7 @@
         <v>125703095</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>125704111</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>125703079</v>
       </c>
       <c r="B37" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4204,7 +4204,7 @@
         <v>125703091</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>125703104</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4395,10 +4395,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125703088</v>
+        <v>125703087</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>501841</v>
+        <v>501873</v>
       </c>
       <c r="R40" t="n">
-        <v>6762704</v>
+        <v>6762669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4492,10 +4492,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125703087</v>
+        <v>125703088</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>501873</v>
+        <v>501841</v>
       </c>
       <c r="R41" t="n">
-        <v>6762669</v>
+        <v>6762704</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4592,7 +4592,7 @@
         <v>125703093</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
         <v>125703098</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4783,10 +4783,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125703100</v>
+        <v>125703094</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>501827</v>
+        <v>501903</v>
       </c>
       <c r="R44" t="n">
-        <v>6762616</v>
+        <v>6762639</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4880,10 +4880,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125703094</v>
+        <v>125703100</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>501903</v>
+        <v>501827</v>
       </c>
       <c r="R45" t="n">
-        <v>6762639</v>
+        <v>6762616</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4980,7 +4980,7 @@
         <v>125703099</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>125703092</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>125703103</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         <v>125703090</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
